--- a/companies/ssi/financials/ssi_model_2026-08-14.xlsx
+++ b/companies/ssi/financials/ssi_model_2026-08-14.xlsx
@@ -1415,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J11"/>
+  <dimension ref="B2:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1527,38 +1527,40 @@
     <row r="8">
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Valuation at last completed round</t>
+          <t>Chief executive</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="30" t="n">
-        <v>31</v>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Ilya Sutskever (CEO and Chief Scientist); Daniel Gross was C</t>
+        </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="J8" s="29" t="inlineStr">
         <is>
-          <t>canonical ~$30-32B, midpoint carried; NOT re-pulled at the Jul 16 refresh</t>
+          <t>PitchBook deal records 340484-77T and 284541-22T</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Equity raised</t>
+          <t>Valuation at last completed round</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr"/>
       <c r="D9" s="30" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -1567,28 +1569,28 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="J9" s="29" t="inlineStr">
         <is>
-          <t>canonical</t>
+          <t>canonical ~$30-32B, midpoint carried; NOT re-pulled at the Jul 16 refresh</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Annualised revenue</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr"/>
       <c r="D10" s="30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1598,31 +1600,191 @@
       </c>
       <c r="J10" s="29" t="inlineStr">
         <is>
-          <t>pre-revenue</t>
+          <t>PitchBook deal 271260-55T (Early Stage VC)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Quality score (composite)</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr"/>
       <c r="D11" s="30" t="n">
+        <v>32</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J11" s="29" t="inlineStr">
+        <is>
+          <t>PitchBook deal 284541-22T (Early Stage VC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Equity raised</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr"/>
+      <c r="D12" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J12" s="29" t="inlineStr">
+        <is>
+          <t>canonical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Last completed round</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>$6.0B early-stage round at $32B post (2025-04-11), led by Gr</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J13" s="29" t="inlineStr">
+        <is>
+          <t>PitchBook deal 284541-22T</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Raised to date ($bn)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr"/>
+      <c r="D14" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J14" s="29" t="inlineStr">
+        <is>
+          <t>PitchBook Raised to Date, deal 284541-22T</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Rumored round</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Closed on $5B of an undisclosed target from Nvidia, announce</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J15" s="29" t="inlineStr">
+        <is>
+          <t>PitchBook deal 340484-77T (status Announced/In Progress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Annualised revenue</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr"/>
+      <c r="D16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J16" s="29" t="inlineStr">
+        <is>
+          <t>pre-revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Quality score (composite)</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr"/>
+      <c r="D17" s="30" t="n">
         <v>2.3</v>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="J11" s="29" t="inlineStr">
+      <c r="J17" s="29" t="inlineStr">
         <is>
           <t>internal AIBQ v3.0 (this desk)</t>
         </is>
